--- a/data/trans_dic/BARTHEL_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/BARTHEL_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,1</t>
+          <t>1,9; 6,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 11,46</t>
+          <t>5,23; 11,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,79</t>
+          <t>3,71; 8,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 8,63</t>
+          <t>4,45; 8,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,1</t>
+          <t>4,76; 10,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,75</t>
+          <t>8,67; 16,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,06</t>
+          <t>6,3; 12,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,29</t>
+          <t>6,48; 10,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,29</t>
+          <t>3,85; 7,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,75</t>
+          <t>7,88; 12,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 9,66</t>
+          <t>5,7; 9,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,77</t>
+          <t>5,94; 8,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 19,35</t>
+          <t>10,25; 19,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 30,03</t>
+          <t>17,72; 30,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 24,9</t>
+          <t>15,34; 24,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 26,15</t>
+          <t>17,4; 24,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,64; 24,62</t>
+          <t>15,65; 24,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,84; 44,02</t>
+          <t>33,83; 43,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7; 39,8</t>
+          <t>27,99; 39,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,87; 40,65</t>
+          <t>33,64; 40,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,22</t>
+          <t>14,49; 21,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,31; 36,74</t>
+          <t>29,01; 37,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 32,14</t>
+          <t>24,56; 32,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,6; 33,78</t>
+          <t>28,22; 33,27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,41</t>
+          <t>6,2; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,09</t>
+          <t>11,98; 18,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,08; 15,29</t>
+          <t>10,62; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,11</t>
+          <t>11,15; 16,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,52</t>
+          <t>22,45; 28,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,49</t>
+          <t>18,76; 25,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 23,51</t>
+          <t>20,85; 25,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,06</t>
+          <t>9,36; 12,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,77</t>
+          <t>18,97; 23,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,37; 19,56</t>
+          <t>15,45; 19,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,11</t>
+          <t>16,9; 20,01</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) (tasa de respuesta: 100,0%)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>61177</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5496; 17835</t>
+          <t>5560; 17789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16249; 35500</t>
+          <t>16200; 36172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11634; 29372</t>
+          <t>12399; 29641</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17254; 31776</t>
+          <t>18130; 34185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15817; 34641</t>
+          <t>16336; 34398</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30499; 55745</t>
+          <t>30699; 57179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24260; 49351</t>
+          <t>23797; 46214</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12686; 50218</t>
+          <t>28273; 45161</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23813; 46317</t>
+          <t>24447; 47978</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51906; 84640</t>
+          <t>52308; 84481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40323; 68767</t>
+          <t>40619; 67885</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25886; 75661</t>
+          <t>50098; 73006</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>64887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>156555</t>
+          <t>170882</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>217603</t>
+          <t>235770</t>
         </is>
       </c>
     </row>
@@ -1571,62 +1571,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21168; 40605</t>
+          <t>21517; 41668</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45648; 75020</t>
+          <t>44268; 75491</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40183; 63999</t>
+          <t>39413; 63167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51312; 73272</t>
+          <t>53454; 76702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52213; 82211</t>
+          <t>52250; 83193</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>131612; 171245</t>
+          <t>131588; 170900</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>114864; 159280</t>
+          <t>111988; 156082</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>142916; 171516</t>
+          <t>154957; 186646</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79434; 115372</t>
+          <t>78790; 116007</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>187253; 234725</t>
+          <t>185311; 237426</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163044; 211214</t>
+          <t>161412; 212026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>200796; 237144</t>
+          <t>216675; 255453</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29182; 52301</t>
+          <t>31162; 53936</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65275; 101241</t>
+          <t>67035; 102984</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56165; 86052</t>
+          <t>56185; 86038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71839; 99136</t>
+          <t>75881; 105557</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73382; 109071</t>
+          <t>75498; 111199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>171211; 219312</t>
+          <t>166780; 215353</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>145837; 198271</t>
+          <t>145972; 195591</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100373; 241687</t>
+          <t>187084; 226763</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109799; 153994</t>
+          <t>110431; 153159</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246971; 309586</t>
+          <t>247130; 306910</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210422; 267800</t>
+          <t>211551; 270154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>172260; 320343</t>
+          <t>272374; 322447</t>
         </is>
       </c>
     </row>
